--- a/docs/verification/BBW_SBW_Requirements_Traceability_FR.xlsx
+++ b/docs/verification/BBW_SBW_Requirements_Traceability_FR.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Plan" sheetId="1" r:id="R880bc6be3a234fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="2" r:id="Rb02f5188beab4e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Catalog" sheetId="3" r:id="R8222e378b09d4b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Plan" sheetId="1" r:id="Reecb23440395493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="2" r:id="R06b9622361214f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Catalog" sheetId="3" r:id="R2190a724bc8b4a47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -156,7 +156,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -211,6 +211,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEEAFB"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -347,7 +357,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -701,11 +711,20 @@
     <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="26">
+  <x:dxfs count="27">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -974,6 +993,17 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF087A65"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F5F1"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -1015,18 +1045,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestCatalogTable" displayName="TestCatalogTable" ref="A4:J20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestCatalogTable" displayName="TestCatalogTable" ref="A4:J23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
-    <x:tableColumn id="1" name="Test ID"/>
+    <x:tableColumn id="1" name="ID du test"/>
     <x:tableColumn id="2" name="Type"/>
-    <x:tableColumn id="3" name="Name"/>
-    <x:tableColumn id="4" name="Demand Fx [N]"/>
-    <x:tableColumn id="5" name="Demand Mz [N m]"/>
-    <x:tableColumn id="6" name="Fault scenario"/>
-    <x:tableColumn id="7" name="Fault time [s]"/>
-    <x:tableColumn id="8" name="Requirements"/>
-    <x:tableColumn id="9" name="Primary evidence"/>
-    <x:tableColumn id="10" name="Status"/>
+    <x:tableColumn id="3" name="Nom"/>
+    <x:tableColumn id="4" name="Demande Fx [N]"/>
+    <x:tableColumn id="5" name="Demande Mz [N m]"/>
+    <x:tableColumn id="6" name="Scénario de défaut"/>
+    <x:tableColumn id="7" name="Instant du défaut [s]"/>
+    <x:tableColumn id="8" name="Exigences"/>
+    <x:tableColumn id="9" name="Preuve principale"/>
+    <x:tableColumn id="10" name="État"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -4150,7 +4180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5e5f753bdfa4fee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ac29be27b444f48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4599,7 +4629,7 @@
         <x:v>G3</x:v>
       </x:c>
       <x:c r="L13" s="95" t="str">
-        <x:v>Estimation statique actuelle : 16,6 %</x:v>
+        <x:v>Estimation statique limitée par l'adhérence : 37,6 %</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -4734,7 +4764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5955ac4441eb4791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ad1ee16b3cc4da2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4746,16 +4776,16 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="35" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4776,7 +4806,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="89" t="str">
-        <x:v>Exécuter validation/run_validation_campaign.m pour régénérer les résultats et les figures.</x:v>
+        <x:v>Exécuter run_project_validation.m pour régénérer les preuves du modèle et de l'allocateur.</x:v>
       </x:c>
       <x:c r="B2" s="89"/>
       <x:c r="C2" s="89"/>
@@ -4804,7 +4834,7 @@
       <x:c r="K3" s="90"/>
       <x:c r="L3" s="90"/>
     </x:row>
-    <x:row r="4" ht="28" customHeight="1">
+    <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="93" t="str">
         <x:v>ID du test</x:v>
       </x:c>
@@ -5331,6 +5361,90 @@
       </x:c>
       <x:c r="K20" s="90"/>
       <x:c r="L20" s="90"/>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="124" t="str">
+        <x:v>PLANT-BRK-01</x:v>
+      </x:c>
+      <x:c r="B21" s="124" t="str">
+        <x:v>Modèle</x:v>
+      </x:c>
+      <x:c r="C21" s="124" t="str">
+        <x:v>Freinage rectiligne symétrique</x:v>
+      </x:c>
+      <x:c r="D21" s="124" t="n">
+        <x:v>-6000</x:v>
+      </x:c>
+      <x:c r="E21" s="124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="124" t="str">
+        <x:v>allocateur contourné</x:v>
+      </x:c>
+      <x:c r="G21" s="124"/>
+      <x:c r="H21" s="124" t="str">
+        <x:v>Modèle G2</x:v>
+      </x:c>
+      <x:c r="I21" s="124" t="str">
+        <x:v>plant/PLANT-BRK-01/vehicle_response.png</x:v>
+      </x:c>
+      <x:c r="J21" s="124" t="str">
+        <x:v>Automatisé</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="A22" s="125" t="str">
+        <x:v>PLANT-STR-01</x:v>
+      </x:c>
+      <x:c r="B22" s="125" t="str">
+        <x:v>Modèle</x:v>
+      </x:c>
+      <x:c r="C22" s="125" t="str">
+        <x:v>Échelon positif de direction de un degré</x:v>
+      </x:c>
+      <x:c r="D22" s="125"/>
+      <x:c r="E22" s="125"/>
+      <x:c r="F22" s="125" t="str">
+        <x:v>allocateur contourné</x:v>
+      </x:c>
+      <x:c r="G22" s="125"/>
+      <x:c r="H22" s="125" t="str">
+        <x:v>Modèle G2</x:v>
+      </x:c>
+      <x:c r="I22" s="125" t="str">
+        <x:v>plant/PLANT-STR-01/vehicle_response.png</x:v>
+      </x:c>
+      <x:c r="J22" s="125" t="str">
+        <x:v>Automatisé</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="124" t="str">
+        <x:v>PLANT-CMB-01</x:v>
+      </x:c>
+      <x:c r="B23" s="124" t="str">
+        <x:v>Modèle</x:v>
+      </x:c>
+      <x:c r="C23" s="124" t="str">
+        <x:v>Freinage et direction combinés</x:v>
+      </x:c>
+      <x:c r="D23" s="124" t="n">
+        <x:v>-4000</x:v>
+      </x:c>
+      <x:c r="E23" s="124"/>
+      <x:c r="F23" s="124" t="str">
+        <x:v>allocateur contourné</x:v>
+      </x:c>
+      <x:c r="G23" s="124"/>
+      <x:c r="H23" s="124" t="str">
+        <x:v>Modèle G2</x:v>
+      </x:c>
+      <x:c r="I23" s="124" t="str">
+        <x:v>plant/PLANT-CMB-01/vehicle_response.png</x:v>
+      </x:c>
+      <x:c r="J23" s="124" t="str">
+        <x:v>Automatisé</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5342,9 +5456,12 @@
     <x:cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="Planifié"/>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J21:J23">
+    <x:cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Automatisé"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46a501dc5c404b49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9582a391c9c5472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>